--- a/data/file_generation/input/data_383/dx60 周岁以上人员名单.xlsx
+++ b/data/file_generation/input/data_383/dx60 周岁以上人员名单.xlsx
@@ -1,15 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_61FDF6281F24DF76A4C2A4E41124F3909AB44E24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7CDB10-38D6-418C-BABB-AB7760C7F1FF}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -58,475 +75,475 @@
     <t>user_40</t>
   </si>
   <si>
+    <t>******195503187270</t>
+  </si>
+  <si>
+    <t>四级残疾人</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>肢体残疾</t>
+  </si>
+  <si>
+    <t>2020年残疾人生活补贴</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>解放中路</t>
+  </si>
+  <si>
     <t>user_29</t>
   </si>
   <si>
+    <t>******196306020492</t>
+  </si>
+  <si>
+    <t>二级残疾人</t>
+  </si>
+  <si>
+    <t>视力残疾</t>
+  </si>
+  <si>
     <t>user_41</t>
   </si>
   <si>
+    <t>******196101102558</t>
+  </si>
+  <si>
+    <t>三级残疾人</t>
+  </si>
+  <si>
     <t>user_42</t>
   </si>
   <si>
+    <t>******196510273438</t>
+  </si>
+  <si>
     <t>user_43</t>
   </si>
   <si>
+    <t>******193002037806</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
     <t>user_44</t>
   </si>
   <si>
+    <t>******196311082428</t>
+  </si>
+  <si>
     <t>user_45</t>
   </si>
   <si>
+    <t>******195111052561</t>
+  </si>
+  <si>
+    <t>一级残疾人</t>
+  </si>
+  <si>
     <t>user_46</t>
   </si>
   <si>
+    <t>******195706190023</t>
+  </si>
+  <si>
     <t>user_38</t>
   </si>
   <si>
+    <t>******195011076339</t>
+  </si>
+  <si>
+    <t>智力残疾</t>
+  </si>
+  <si>
     <t>user_47</t>
   </si>
   <si>
+    <t>******195310011164</t>
+  </si>
+  <si>
+    <t>多重残疾</t>
+  </si>
+  <si>
     <t>user_48</t>
   </si>
   <si>
+    <t>******195812295531</t>
+  </si>
+  <si>
     <t>user_30</t>
   </si>
   <si>
+    <t>******194501210807</t>
+  </si>
+  <si>
+    <t>解放南路</t>
+  </si>
+  <si>
     <t>user_49</t>
   </si>
   <si>
+    <t>******196403250513</t>
+  </si>
+  <si>
+    <t>言语残疾</t>
+  </si>
+  <si>
     <t>user_25</t>
   </si>
   <si>
+    <t>******196310100495</t>
+  </si>
+  <si>
     <t>user_50</t>
   </si>
   <si>
+    <t>******196510220029</t>
+  </si>
+  <si>
+    <t>解放北路</t>
+  </si>
+  <si>
     <t>user_51</t>
   </si>
   <si>
+    <t>******195607133437</t>
+  </si>
+  <si>
+    <t>解放路</t>
+  </si>
+  <si>
     <t>user_52</t>
   </si>
   <si>
+    <t>******196305100036</t>
+  </si>
+  <si>
+    <t>听力残疾</t>
+  </si>
+  <si>
+    <t>西街</t>
+  </si>
+  <si>
     <t>user_19</t>
   </si>
   <si>
+    <t>******194901090031</t>
+  </si>
+  <si>
     <t>user_18</t>
   </si>
   <si>
+    <t>******195910297370</t>
+  </si>
+  <si>
     <t>user_53</t>
   </si>
   <si>
+    <t>******195202060022</t>
+  </si>
+  <si>
     <t>user_54</t>
   </si>
   <si>
+    <t>******195410280011</t>
+  </si>
+  <si>
     <t>user_55</t>
   </si>
   <si>
+    <t>******193802132553</t>
+  </si>
+  <si>
     <t>user_56</t>
   </si>
   <si>
+    <t>******19570313005X</t>
+  </si>
+  <si>
     <t>user_10</t>
   </si>
   <si>
+    <t>******196507165740</t>
+  </si>
+  <si>
+    <t>东街</t>
+  </si>
+  <si>
     <t>user_16</t>
   </si>
   <si>
+    <t>******196205066053</t>
+  </si>
+  <si>
     <t>user_57</t>
   </si>
   <si>
+    <t>******19520512049X</t>
+  </si>
+  <si>
+    <t>南街</t>
+  </si>
+  <si>
     <t>user_58</t>
   </si>
   <si>
+    <t>******196207167827</t>
+  </si>
+  <si>
     <t>user_59</t>
   </si>
   <si>
+    <t>******19390602344X</t>
+  </si>
+  <si>
+    <t>北街</t>
+  </si>
+  <si>
     <t>user_60</t>
   </si>
   <si>
+    <t>******196511280015</t>
+  </si>
+  <si>
     <t>user_61</t>
   </si>
   <si>
+    <t>******195608282565</t>
+  </si>
+  <si>
     <t>user_62</t>
   </si>
   <si>
+    <t>******194202037258</t>
+  </si>
+  <si>
     <t>user_63</t>
   </si>
   <si>
+    <t>******194206142418</t>
+  </si>
+  <si>
     <t>user_64</t>
   </si>
   <si>
+    <t>******196509093544</t>
+  </si>
+  <si>
+    <t>精神残疾</t>
+  </si>
+  <si>
+    <t>项山路</t>
+  </si>
+  <si>
     <t>user_20</t>
   </si>
   <si>
+    <t>******193505027503</t>
+  </si>
+  <si>
     <t>user_65</t>
   </si>
   <si>
+    <t>******19590129256X</t>
+  </si>
+  <si>
     <t>user_66</t>
   </si>
   <si>
+    <t>******196212010066</t>
+  </si>
+  <si>
     <t>user_67</t>
   </si>
   <si>
+    <t>******194209293545</t>
+  </si>
+  <si>
+    <t>石岭大道</t>
+  </si>
+  <si>
     <t>user_68</t>
   </si>
   <si>
+    <t>******19630428008X</t>
+  </si>
+  <si>
+    <t>滨河路</t>
+  </si>
+  <si>
     <t>user_69</t>
   </si>
   <si>
+    <t>******196304081013</t>
+  </si>
+  <si>
+    <t>代家湾</t>
+  </si>
+  <si>
     <t>user_70</t>
   </si>
   <si>
+    <t>******196503057796</t>
+  </si>
+  <si>
     <t>user_71</t>
   </si>
   <si>
+    <t>******194501080205</t>
+  </si>
+  <si>
     <t>user_72</t>
   </si>
   <si>
+    <t>******194504166522</t>
+  </si>
+  <si>
     <t>user_73</t>
   </si>
   <si>
+    <t>******195002235895</t>
+  </si>
+  <si>
     <t>user_21</t>
   </si>
   <si>
+    <t>******193901040021</t>
+  </si>
+  <si>
+    <t>上城壕</t>
+  </si>
+  <si>
     <t>user_74</t>
   </si>
   <si>
+    <t>******194510092574</t>
+  </si>
+  <si>
     <t>user_75</t>
   </si>
   <si>
+    <t>******195008162367</t>
+  </si>
+  <si>
+    <t>板桥街</t>
+  </si>
+  <si>
     <t>user_76</t>
   </si>
   <si>
+    <t>******196408260059</t>
+  </si>
+  <si>
     <t>user_77</t>
   </si>
   <si>
+    <t>******195805130034</t>
+  </si>
+  <si>
     <t>user_15</t>
   </si>
   <si>
+    <t>******195205050014</t>
+  </si>
+  <si>
+    <t>新市街</t>
+  </si>
+  <si>
     <t>user_78</t>
   </si>
   <si>
+    <t>******195905063721</t>
+  </si>
+  <si>
     <t>user_79</t>
   </si>
   <si>
+    <t>******195604100015</t>
+  </si>
+  <si>
     <t>user_80</t>
   </si>
   <si>
+    <t>******196312165532</t>
+  </si>
+  <si>
+    <t>鱼禅寺</t>
+  </si>
+  <si>
     <t>user_81</t>
   </si>
   <si>
+    <t>******196312090024</t>
+  </si>
+  <si>
+    <t>学坝街</t>
+  </si>
+  <si>
     <t>user_26</t>
   </si>
   <si>
+    <t>******19630714725X</t>
+  </si>
+  <si>
     <t>user_82</t>
   </si>
   <si>
+    <t>******196306110025</t>
+  </si>
+  <si>
+    <t>牌立湾</t>
+  </si>
+  <si>
     <t>user_83</t>
   </si>
   <si>
+    <t>******195001090495</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
     <t>user_84</t>
   </si>
   <si>
+    <t>******195804293536</t>
+  </si>
+  <si>
     <t>user_85</t>
   </si>
   <si>
+    <t>******196207153433</t>
+  </si>
+  <si>
     <t>user_86</t>
   </si>
   <si>
+    <t>******196210313434</t>
+  </si>
+  <si>
     <t>user_87</t>
   </si>
   <si>
+    <t>******195607093471</t>
+  </si>
+  <si>
     <t>user_88</t>
   </si>
   <si>
-    <t>******195503187270</t>
-  </si>
-  <si>
-    <t>******196306020492</t>
-  </si>
-  <si>
-    <t>******196101102558</t>
-  </si>
-  <si>
-    <t>******196510273438</t>
-  </si>
-  <si>
-    <t>******193002037806</t>
-  </si>
-  <si>
-    <t>******196311082428</t>
-  </si>
-  <si>
-    <t>******195111052561</t>
-  </si>
-  <si>
-    <t>******195706190023</t>
-  </si>
-  <si>
-    <t>******195011076339</t>
-  </si>
-  <si>
-    <t>******195310011164</t>
-  </si>
-  <si>
-    <t>******195812295531</t>
-  </si>
-  <si>
-    <t>******194501210807</t>
-  </si>
-  <si>
-    <t>******196403250513</t>
-  </si>
-  <si>
-    <t>******196310100495</t>
-  </si>
-  <si>
-    <t>******196510220029</t>
-  </si>
-  <si>
-    <t>******195607133437</t>
-  </si>
-  <si>
-    <t>******196305100036</t>
-  </si>
-  <si>
-    <t>******194901090031</t>
-  </si>
-  <si>
-    <t>******195910297370</t>
-  </si>
-  <si>
-    <t>******195202060022</t>
-  </si>
-  <si>
-    <t>******195410280011</t>
-  </si>
-  <si>
-    <t>******193802132553</t>
-  </si>
-  <si>
-    <t>******19570313005X</t>
-  </si>
-  <si>
-    <t>******196507165740</t>
-  </si>
-  <si>
-    <t>******196205066053</t>
-  </si>
-  <si>
-    <t>******19520512049X</t>
-  </si>
-  <si>
-    <t>******196207167827</t>
-  </si>
-  <si>
-    <t>******19390602344X</t>
-  </si>
-  <si>
-    <t>******196511280015</t>
-  </si>
-  <si>
-    <t>******195608282565</t>
-  </si>
-  <si>
-    <t>******194202037258</t>
-  </si>
-  <si>
-    <t>******194206142418</t>
-  </si>
-  <si>
-    <t>******196509093544</t>
-  </si>
-  <si>
-    <t>******193505027503</t>
-  </si>
-  <si>
-    <t>******19590129256X</t>
-  </si>
-  <si>
-    <t>******196212010066</t>
-  </si>
-  <si>
-    <t>******194209293545</t>
-  </si>
-  <si>
-    <t>******19630428008X</t>
-  </si>
-  <si>
-    <t>******196304081013</t>
-  </si>
-  <si>
-    <t>******196503057796</t>
-  </si>
-  <si>
-    <t>******194501080205</t>
-  </si>
-  <si>
-    <t>******194504166522</t>
-  </si>
-  <si>
-    <t>******195002235895</t>
-  </si>
-  <si>
-    <t>******193901040021</t>
-  </si>
-  <si>
-    <t>******194510092574</t>
-  </si>
-  <si>
-    <t>******195008162367</t>
-  </si>
-  <si>
-    <t>******196408260059</t>
-  </si>
-  <si>
-    <t>******195805130034</t>
-  </si>
-  <si>
-    <t>******195205050014</t>
-  </si>
-  <si>
-    <t>******195905063721</t>
-  </si>
-  <si>
-    <t>******195604100015</t>
-  </si>
-  <si>
-    <t>******196312165532</t>
-  </si>
-  <si>
-    <t>******196312090024</t>
-  </si>
-  <si>
-    <t>******19630714725X</t>
-  </si>
-  <si>
-    <t>******196306110025</t>
-  </si>
-  <si>
-    <t>******195001090495</t>
-  </si>
-  <si>
-    <t>******195804293536</t>
-  </si>
-  <si>
-    <t>******196207153433</t>
-  </si>
-  <si>
-    <t>******196210313434</t>
-  </si>
-  <si>
-    <t>******195607093471</t>
-  </si>
-  <si>
     <t>******195209162419</t>
-  </si>
-  <si>
-    <t>四级残疾人</t>
-  </si>
-  <si>
-    <t>二级残疾人</t>
-  </si>
-  <si>
-    <t>三级残疾人</t>
-  </si>
-  <si>
-    <t>一级残疾人</t>
-  </si>
-  <si>
-    <t>2025-10</t>
-  </si>
-  <si>
-    <t>肢体残疾</t>
-  </si>
-  <si>
-    <t>视力残疾</t>
-  </si>
-  <si>
-    <t>智力残疾</t>
-  </si>
-  <si>
-    <t>多重残疾</t>
-  </si>
-  <si>
-    <t>言语残疾</t>
-  </si>
-  <si>
-    <t>听力残疾</t>
-  </si>
-  <si>
-    <t>精神残疾</t>
-  </si>
-  <si>
-    <t>2020年残疾人生活补贴</t>
-  </si>
-  <si>
-    <t>男</t>
-  </si>
-  <si>
-    <t>女</t>
-  </si>
-  <si>
-    <t>解放中路</t>
-  </si>
-  <si>
-    <t>解放南路</t>
-  </si>
-  <si>
-    <t>解放北路</t>
-  </si>
-  <si>
-    <t>解放路</t>
-  </si>
-  <si>
-    <t>西街</t>
-  </si>
-  <si>
-    <t>东街</t>
-  </si>
-  <si>
-    <t>南街</t>
-  </si>
-  <si>
-    <t>北街</t>
-  </si>
-  <si>
-    <t>项山路</t>
-  </si>
-  <si>
-    <t>石岭大道</t>
-  </si>
-  <si>
-    <t>滨河路</t>
-  </si>
-  <si>
-    <t>代家湾</t>
-  </si>
-  <si>
-    <t>上城壕</t>
-  </si>
-  <si>
-    <t>板桥街</t>
-  </si>
-  <si>
-    <t>新市街</t>
-  </si>
-  <si>
-    <t>鱼禅寺</t>
-  </si>
-  <si>
-    <t>学坝街</t>
-  </si>
-  <si>
-    <t>牌立湾</t>
-  </si>
-  <si>
-    <t>其他</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -586,17 +603,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -634,7 +659,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -668,6 +693,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -702,9 +728,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -877,9 +904,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="36.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
@@ -933,31 +963,31 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
       <c r="I2" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -971,34 +1001,34 @@
         <v>18834</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
       <c r="I3" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L3" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -1012,34 +1042,34 @@
         <v>18474</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -1053,34 +1083,34 @@
         <v>18508</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K5" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -1094,34 +1124,34 @@
         <v>18688</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>95</v>
       </c>
       <c r="F6" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -1135,34 +1165,34 @@
         <v>19301</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -1176,34 +1206,34 @@
         <v>18236</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L8" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -1217,34 +1247,34 @@
         <v>18464</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L9" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -1258,34 +1288,34 @@
         <v>18747</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L10" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -1299,34 +1329,34 @@
         <v>18443</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="J11" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L11" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -1340,34 +1370,34 @@
         <v>18471</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E12">
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L12" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="M12">
         <v>1</v>
@@ -1381,34 +1411,34 @@
         <v>18713</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="M13">
         <v>2</v>
@@ -1422,34 +1452,34 @@
         <v>18840</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="E14">
         <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="M14">
         <v>2</v>
@@ -1463,34 +1493,34 @@
         <v>18490</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="E15">
         <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L15" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="M15">
         <v>2</v>
@@ -1504,34 +1534,34 @@
         <v>18506</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
       <c r="I16" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L16" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="M16">
         <v>3</v>
@@ -1545,34 +1575,34 @@
         <v>19272</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J17" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L17" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="M17">
         <v>4</v>
@@ -1586,34 +1616,34 @@
         <v>18255</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="E18">
         <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="J18" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L18" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -1627,34 +1657,34 @@
         <v>19215</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E19">
         <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L19" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -1668,34 +1698,34 @@
         <v>18253</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E20">
         <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L20" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -1709,34 +1739,34 @@
         <v>19235</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J21" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L21" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -1750,34 +1780,34 @@
         <v>18450</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E22">
         <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J22" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L22" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -1791,34 +1821,34 @@
         <v>18693</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E23">
         <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="J23" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L23" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -1832,34 +1862,34 @@
         <v>18462</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E24">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H24">
         <v>100</v>
       </c>
       <c r="I24" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J24" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L24" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -1873,34 +1903,34 @@
         <v>18620</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E25">
         <v>60</v>
       </c>
       <c r="F25" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H25">
         <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J25" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L25" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="M25">
         <v>11</v>
@@ -1914,34 +1944,34 @@
         <v>18821</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E26">
         <v>63</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H26">
         <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J26" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K26" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L26" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="M26">
         <v>11</v>
@@ -1955,34 +1985,34 @@
         <v>18762</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E27">
         <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J27" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K27" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L27" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="M27">
         <v>12</v>
@@ -1996,34 +2026,34 @@
         <v>18823</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E28">
         <v>63</v>
       </c>
       <c r="F28" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="J28" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L28" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="M28">
         <v>12</v>
@@ -2037,34 +2067,34 @@
         <v>18382</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E29">
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H29">
         <v>100</v>
       </c>
       <c r="I29" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J29" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L29" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="M29">
         <v>13</v>
@@ -2078,34 +2108,34 @@
         <v>18261</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E30">
         <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H30">
         <v>100</v>
       </c>
       <c r="I30" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J30" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L30" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="M30">
         <v>13</v>
@@ -2119,34 +2149,34 @@
         <v>19273</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E31">
         <v>69</v>
       </c>
       <c r="F31" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J31" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L31" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="M31">
         <v>13</v>
@@ -2160,34 +2190,34 @@
         <v>19187</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E32">
         <v>83</v>
       </c>
       <c r="F32" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="I32" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J32" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L32" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="M32">
         <v>13</v>
@@ -2201,34 +2231,34 @@
         <v>18386</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E33">
         <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J33" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K33" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L33" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="M33">
         <v>13</v>
@@ -2242,34 +2272,34 @@
         <v>18504</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H34">
         <v>100</v>
       </c>
       <c r="I34" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="J34" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L34" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="M34">
         <v>20</v>
@@ -2283,34 +2313,34 @@
         <v>18377</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E35">
         <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H35">
         <v>100</v>
       </c>
       <c r="I35" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J35" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L35" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="M35">
         <v>20</v>
@@ -2324,34 +2354,34 @@
         <v>18812</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E36">
         <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G36" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J36" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L36" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="M36">
         <v>20</v>
@@ -2365,34 +2395,34 @@
         <v>18254</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37">
         <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H37">
         <v>100</v>
       </c>
       <c r="I37" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="J37" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K37" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L37" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="M37">
         <v>20</v>
@@ -2406,7 +2436,7 @@
         <v>19189</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
         <v>110</v>
@@ -2415,25 +2445,25 @@
         <v>83</v>
       </c>
       <c r="F38" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H38">
         <v>100</v>
       </c>
       <c r="I38" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J38" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K38" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L38" t="s">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="M38">
         <v>21</v>
@@ -2447,34 +2477,34 @@
         <v>18833</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E39">
         <v>62</v>
       </c>
       <c r="F39" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H39">
         <v>100</v>
       </c>
       <c r="I39" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="J39" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K39" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L39" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="M39">
         <v>22</v>
@@ -2488,34 +2518,34 @@
         <v>18830</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E40">
         <v>62</v>
       </c>
       <c r="F40" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H40">
         <v>100</v>
       </c>
       <c r="I40" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J40" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K40" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L40" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="M40">
         <v>30</v>
@@ -2529,34 +2559,34 @@
         <v>18259</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E41">
         <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H41">
         <v>100</v>
       </c>
       <c r="I41" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J41" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L41" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="M41">
         <v>30</v>
@@ -2570,34 +2600,34 @@
         <v>19198</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="D42" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E42">
         <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H42">
         <v>100</v>
       </c>
       <c r="I42" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J42" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K42" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L42" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="M42">
         <v>30</v>
@@ -2611,34 +2641,34 @@
         <v>18394</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E43">
         <v>80</v>
       </c>
       <c r="F43" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H43">
         <v>100</v>
       </c>
       <c r="I43" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J43" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K43" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L43" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="M43">
         <v>30</v>
@@ -2652,34 +2682,34 @@
         <v>18233</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="D44" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E44">
         <v>75</v>
       </c>
       <c r="F44" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G44" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H44">
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K44" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L44" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="M44">
         <v>30</v>
@@ -2693,34 +2723,34 @@
         <v>18699</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E45">
         <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J45" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K45" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L45" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="M45">
         <v>31</v>
@@ -2734,34 +2764,34 @@
         <v>18226</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E46">
         <v>80</v>
       </c>
       <c r="F46" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G46" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H46">
         <v>100</v>
       </c>
       <c r="I46" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J46" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L46" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="M46">
         <v>31</v>
@@ -2775,34 +2805,34 @@
         <v>18745</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="D47" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="E47">
         <v>75</v>
       </c>
       <c r="F47" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H47">
         <v>100</v>
       </c>
       <c r="I47" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="J47" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K47" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L47" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="M47">
         <v>32</v>
@@ -2816,34 +2846,34 @@
         <v>18499</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E48">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H48">
         <v>100</v>
       </c>
       <c r="I48" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J48" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L48" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="M48">
         <v>32</v>
@@ -2857,34 +2887,34 @@
         <v>18470</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="D49" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E49">
         <v>67</v>
       </c>
       <c r="F49" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G49" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H49">
         <v>100</v>
       </c>
       <c r="I49" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L49" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="M49">
         <v>32</v>
@@ -2898,34 +2928,34 @@
         <v>18761</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="E50">
         <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H50">
         <v>100</v>
       </c>
       <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
+        <v>18</v>
+      </c>
+      <c r="K50" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" t="s">
         <v>140</v>
-      </c>
-      <c r="J50" t="s">
-        <v>147</v>
-      </c>
-      <c r="K50" t="s">
-        <v>148</v>
-      </c>
-      <c r="L50" t="s">
-        <v>164</v>
       </c>
       <c r="M50">
         <v>33</v>
@@ -2939,34 +2969,34 @@
         <v>18252</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="E51">
         <v>66</v>
       </c>
       <c r="F51" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G51" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H51">
         <v>100</v>
       </c>
       <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" t="s">
+        <v>18</v>
+      </c>
+      <c r="K51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L51" t="s">
         <v>140</v>
-      </c>
-      <c r="J51" t="s">
-        <v>147</v>
-      </c>
-      <c r="K51" t="s">
-        <v>149</v>
-      </c>
-      <c r="L51" t="s">
-        <v>164</v>
       </c>
       <c r="M51">
         <v>33</v>
@@ -2980,34 +3010,34 @@
         <v>18796</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D52" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="E52">
         <v>69</v>
       </c>
       <c r="F52" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H52">
         <v>100</v>
       </c>
       <c r="I52" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J52" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K52" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L52" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="M52">
         <v>33</v>
@@ -3021,34 +3051,34 @@
         <v>18492</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="D53" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="E53">
         <v>62</v>
       </c>
       <c r="F53" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H53">
         <v>100</v>
       </c>
       <c r="I53" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="J53" t="s">
+        <v>18</v>
+      </c>
+      <c r="K53" t="s">
+        <v>19</v>
+      </c>
+      <c r="L53" t="s">
         <v>147</v>
-      </c>
-      <c r="K53" t="s">
-        <v>148</v>
-      </c>
-      <c r="L53" t="s">
-        <v>165</v>
       </c>
       <c r="M53">
         <v>34</v>
@@ -3062,34 +3092,34 @@
         <v>19302</v>
       </c>
       <c r="C54" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E54">
         <v>62</v>
       </c>
       <c r="F54" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H54">
         <v>100</v>
       </c>
       <c r="I54" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J54" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K54" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L54" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="M54">
         <v>35</v>
@@ -3103,34 +3133,34 @@
         <v>19299</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="D55" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="E55">
         <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H55">
         <v>100</v>
       </c>
       <c r="I55" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J55" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L55" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="M55">
         <v>35</v>
@@ -3144,34 +3174,34 @@
         <v>18487</v>
       </c>
       <c r="C56" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E56">
         <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H56">
         <v>100</v>
       </c>
       <c r="I56" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J56" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K56" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="L56" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="M56">
         <v>36</v>
@@ -3185,34 +3215,34 @@
         <v>18743</v>
       </c>
       <c r="C57" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="D57" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="E57">
         <v>75</v>
       </c>
       <c r="F57" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G57" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H57">
         <v>100</v>
       </c>
       <c r="I57" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="J57" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L57" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M57">
         <v>999</v>
@@ -3226,34 +3256,34 @@
         <v>19290</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="D58" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="E58">
         <v>67</v>
       </c>
       <c r="F58" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H58">
         <v>100</v>
       </c>
       <c r="I58" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J58" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K58" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L58" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M58">
         <v>999</v>
@@ -3267,34 +3297,34 @@
         <v>19295</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="E59">
         <v>63</v>
       </c>
       <c r="F59" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H59">
         <v>100</v>
       </c>
       <c r="I59" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K59" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L59" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M59">
         <v>999</v>
@@ -3308,34 +3338,34 @@
         <v>18478</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="D60" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="E60">
         <v>63</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H60">
         <v>100</v>
       </c>
       <c r="I60" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J60" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K60" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L60" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M60">
         <v>999</v>
@@ -3349,34 +3379,34 @@
         <v>19271</v>
       </c>
       <c r="C61" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="D61" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="E61">
         <v>69</v>
       </c>
       <c r="F61" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H61">
         <v>100</v>
       </c>
       <c r="I61" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J61" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L61" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M61">
         <v>999</v>
@@ -3390,34 +3420,34 @@
         <v>19243</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="E62">
         <v>73</v>
       </c>
       <c r="F62" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="H62">
         <v>100</v>
       </c>
       <c r="I62" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="J62" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="K62" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L62" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="M62">
         <v>999</v>
@@ -3429,6 +3459,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -3576,23 +3621,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0986068F-8A5B-49EE-9F40-A58DB927B2D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96F191B-40CB-4280-810C-3CC329D70378}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3600,5 +3630,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96F191B-40CB-4280-810C-3CC329D70378}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0986068F-8A5B-49EE-9F40-A58DB927B2D4}"/>
 </file>
--- a/data/file_generation/input/data_383/dx60 周岁以上人员名单.xlsx
+++ b/data/file_generation/input/data_383/dx60 周岁以上人员名单.xlsx
@@ -1,32 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_61FDF6281F24DF76A4C2A4E41124F3909AB44E24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7CDB10-38D6-418C-BABB-AB7760C7F1FF}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -75,475 +58,475 @@
     <t>user_40</t>
   </si>
   <si>
+    <t>user_29</t>
+  </si>
+  <si>
+    <t>user_41</t>
+  </si>
+  <si>
+    <t>user_42</t>
+  </si>
+  <si>
+    <t>user_43</t>
+  </si>
+  <si>
+    <t>user_44</t>
+  </si>
+  <si>
+    <t>user_45</t>
+  </si>
+  <si>
+    <t>user_46</t>
+  </si>
+  <si>
+    <t>user_38</t>
+  </si>
+  <si>
+    <t>user_47</t>
+  </si>
+  <si>
+    <t>user_48</t>
+  </si>
+  <si>
+    <t>user_30</t>
+  </si>
+  <si>
+    <t>user_49</t>
+  </si>
+  <si>
+    <t>user_25</t>
+  </si>
+  <si>
+    <t>user_50</t>
+  </si>
+  <si>
+    <t>user_51</t>
+  </si>
+  <si>
+    <t>user_52</t>
+  </si>
+  <si>
+    <t>user_19</t>
+  </si>
+  <si>
+    <t>user_18</t>
+  </si>
+  <si>
+    <t>user_53</t>
+  </si>
+  <si>
+    <t>user_54</t>
+  </si>
+  <si>
+    <t>user_55</t>
+  </si>
+  <si>
+    <t>user_56</t>
+  </si>
+  <si>
+    <t>user_10</t>
+  </si>
+  <si>
+    <t>user_16</t>
+  </si>
+  <si>
+    <t>user_57</t>
+  </si>
+  <si>
+    <t>user_58</t>
+  </si>
+  <si>
+    <t>user_59</t>
+  </si>
+  <si>
+    <t>user_60</t>
+  </si>
+  <si>
+    <t>user_61</t>
+  </si>
+  <si>
+    <t>user_62</t>
+  </si>
+  <si>
+    <t>user_63</t>
+  </si>
+  <si>
+    <t>user_64</t>
+  </si>
+  <si>
+    <t>user_20</t>
+  </si>
+  <si>
+    <t>user_65</t>
+  </si>
+  <si>
+    <t>user_66</t>
+  </si>
+  <si>
+    <t>user_67</t>
+  </si>
+  <si>
+    <t>user_68</t>
+  </si>
+  <si>
+    <t>user_69</t>
+  </si>
+  <si>
+    <t>user_70</t>
+  </si>
+  <si>
+    <t>user_71</t>
+  </si>
+  <si>
+    <t>user_72</t>
+  </si>
+  <si>
+    <t>user_73</t>
+  </si>
+  <si>
+    <t>user_21</t>
+  </si>
+  <si>
+    <t>user_74</t>
+  </si>
+  <si>
+    <t>user_75</t>
+  </si>
+  <si>
+    <t>user_76</t>
+  </si>
+  <si>
+    <t>user_77</t>
+  </si>
+  <si>
+    <t>user_15</t>
+  </si>
+  <si>
+    <t>user_78</t>
+  </si>
+  <si>
+    <t>user_79</t>
+  </si>
+  <si>
+    <t>user_80</t>
+  </si>
+  <si>
+    <t>user_81</t>
+  </si>
+  <si>
+    <t>user_26</t>
+  </si>
+  <si>
+    <t>user_82</t>
+  </si>
+  <si>
+    <t>user_83</t>
+  </si>
+  <si>
+    <t>user_84</t>
+  </si>
+  <si>
+    <t>user_85</t>
+  </si>
+  <si>
+    <t>user_86</t>
+  </si>
+  <si>
+    <t>user_87</t>
+  </si>
+  <si>
+    <t>user_88</t>
+  </si>
+  <si>
     <t>******195503187270</t>
   </si>
   <si>
+    <t>******196306020492</t>
+  </si>
+  <si>
+    <t>******196101102558</t>
+  </si>
+  <si>
+    <t>******196510273438</t>
+  </si>
+  <si>
+    <t>******193002037806</t>
+  </si>
+  <si>
+    <t>******196311082428</t>
+  </si>
+  <si>
+    <t>******195111052561</t>
+  </si>
+  <si>
+    <t>******195706190023</t>
+  </si>
+  <si>
+    <t>******195011076339</t>
+  </si>
+  <si>
+    <t>******195310011164</t>
+  </si>
+  <si>
+    <t>******195812295531</t>
+  </si>
+  <si>
+    <t>******194501210807</t>
+  </si>
+  <si>
+    <t>******196403250513</t>
+  </si>
+  <si>
+    <t>******196310100495</t>
+  </si>
+  <si>
+    <t>******196510220029</t>
+  </si>
+  <si>
+    <t>******195607133437</t>
+  </si>
+  <si>
+    <t>******196305100036</t>
+  </si>
+  <si>
+    <t>******194901090031</t>
+  </si>
+  <si>
+    <t>******195910297370</t>
+  </si>
+  <si>
+    <t>******195202060022</t>
+  </si>
+  <si>
+    <t>******195410280011</t>
+  </si>
+  <si>
+    <t>******193802132553</t>
+  </si>
+  <si>
+    <t>******19570313005X</t>
+  </si>
+  <si>
+    <t>******196507165740</t>
+  </si>
+  <si>
+    <t>******196205066053</t>
+  </si>
+  <si>
+    <t>******19520512049X</t>
+  </si>
+  <si>
+    <t>******196207167827</t>
+  </si>
+  <si>
+    <t>******19390602344X</t>
+  </si>
+  <si>
+    <t>******196511280015</t>
+  </si>
+  <si>
+    <t>******195608282565</t>
+  </si>
+  <si>
+    <t>******194202037258</t>
+  </si>
+  <si>
+    <t>******194206142418</t>
+  </si>
+  <si>
+    <t>******196509093544</t>
+  </si>
+  <si>
+    <t>******193505027503</t>
+  </si>
+  <si>
+    <t>******19590129256X</t>
+  </si>
+  <si>
+    <t>******196212010066</t>
+  </si>
+  <si>
+    <t>******194209293545</t>
+  </si>
+  <si>
+    <t>******19630428008X</t>
+  </si>
+  <si>
+    <t>******196304081013</t>
+  </si>
+  <si>
+    <t>******196503057796</t>
+  </si>
+  <si>
+    <t>******194501080205</t>
+  </si>
+  <si>
+    <t>******194504166522</t>
+  </si>
+  <si>
+    <t>******195002235895</t>
+  </si>
+  <si>
+    <t>******193901040021</t>
+  </si>
+  <si>
+    <t>******194510092574</t>
+  </si>
+  <si>
+    <t>******195008162367</t>
+  </si>
+  <si>
+    <t>******196408260059</t>
+  </si>
+  <si>
+    <t>******195805130034</t>
+  </si>
+  <si>
+    <t>******195205050014</t>
+  </si>
+  <si>
+    <t>******195905063721</t>
+  </si>
+  <si>
+    <t>******195604100015</t>
+  </si>
+  <si>
+    <t>******196312165532</t>
+  </si>
+  <si>
+    <t>******196312090024</t>
+  </si>
+  <si>
+    <t>******19630714725X</t>
+  </si>
+  <si>
+    <t>******196306110025</t>
+  </si>
+  <si>
+    <t>******195001090495</t>
+  </si>
+  <si>
+    <t>******195804293536</t>
+  </si>
+  <si>
+    <t>******196207153433</t>
+  </si>
+  <si>
+    <t>******196210313434</t>
+  </si>
+  <si>
+    <t>******195607093471</t>
+  </si>
+  <si>
+    <t>******195209162419</t>
+  </si>
+  <si>
     <t>四级残疾人</t>
   </si>
   <si>
+    <t>二级残疾人</t>
+  </si>
+  <si>
+    <t>三级残疾人</t>
+  </si>
+  <si>
+    <t>一级残疾人</t>
+  </si>
+  <si>
     <t>2025-10</t>
   </si>
   <si>
     <t>肢体残疾</t>
   </si>
   <si>
+    <t>视力残疾</t>
+  </si>
+  <si>
+    <t>智力残疾</t>
+  </si>
+  <si>
+    <t>多重残疾</t>
+  </si>
+  <si>
+    <t>言语残疾</t>
+  </si>
+  <si>
+    <t>听力残疾</t>
+  </si>
+  <si>
+    <t>精神残疾</t>
+  </si>
+  <si>
     <t>2020年残疾人生活补贴</t>
   </si>
   <si>
     <t>男</t>
   </si>
   <si>
+    <t>女</t>
+  </si>
+  <si>
     <t>解放中路</t>
   </si>
   <si>
-    <t>user_29</t>
-  </si>
-  <si>
-    <t>******196306020492</t>
-  </si>
-  <si>
-    <t>二级残疾人</t>
-  </si>
-  <si>
-    <t>视力残疾</t>
-  </si>
-  <si>
-    <t>user_41</t>
-  </si>
-  <si>
-    <t>******196101102558</t>
-  </si>
-  <si>
-    <t>三级残疾人</t>
-  </si>
-  <si>
-    <t>user_42</t>
-  </si>
-  <si>
-    <t>******196510273438</t>
-  </si>
-  <si>
-    <t>user_43</t>
-  </si>
-  <si>
-    <t>******193002037806</t>
-  </si>
-  <si>
-    <t>女</t>
-  </si>
-  <si>
-    <t>user_44</t>
-  </si>
-  <si>
-    <t>******196311082428</t>
-  </si>
-  <si>
-    <t>user_45</t>
-  </si>
-  <si>
-    <t>******195111052561</t>
-  </si>
-  <si>
-    <t>一级残疾人</t>
-  </si>
-  <si>
-    <t>user_46</t>
-  </si>
-  <si>
-    <t>******195706190023</t>
-  </si>
-  <si>
-    <t>user_38</t>
-  </si>
-  <si>
-    <t>******195011076339</t>
-  </si>
-  <si>
-    <t>智力残疾</t>
-  </si>
-  <si>
-    <t>user_47</t>
-  </si>
-  <si>
-    <t>******195310011164</t>
-  </si>
-  <si>
-    <t>多重残疾</t>
-  </si>
-  <si>
-    <t>user_48</t>
-  </si>
-  <si>
-    <t>******195812295531</t>
-  </si>
-  <si>
-    <t>user_30</t>
-  </si>
-  <si>
-    <t>******194501210807</t>
-  </si>
-  <si>
     <t>解放南路</t>
   </si>
   <si>
-    <t>user_49</t>
-  </si>
-  <si>
-    <t>******196403250513</t>
-  </si>
-  <si>
-    <t>言语残疾</t>
-  </si>
-  <si>
-    <t>user_25</t>
-  </si>
-  <si>
-    <t>******196310100495</t>
-  </si>
-  <si>
-    <t>user_50</t>
-  </si>
-  <si>
-    <t>******196510220029</t>
-  </si>
-  <si>
     <t>解放北路</t>
   </si>
   <si>
-    <t>user_51</t>
-  </si>
-  <si>
-    <t>******195607133437</t>
-  </si>
-  <si>
     <t>解放路</t>
   </si>
   <si>
-    <t>user_52</t>
-  </si>
-  <si>
-    <t>******196305100036</t>
-  </si>
-  <si>
-    <t>听力残疾</t>
-  </si>
-  <si>
     <t>西街</t>
   </si>
   <si>
-    <t>user_19</t>
-  </si>
-  <si>
-    <t>******194901090031</t>
-  </si>
-  <si>
-    <t>user_18</t>
-  </si>
-  <si>
-    <t>******195910297370</t>
-  </si>
-  <si>
-    <t>user_53</t>
-  </si>
-  <si>
-    <t>******195202060022</t>
-  </si>
-  <si>
-    <t>user_54</t>
-  </si>
-  <si>
-    <t>******195410280011</t>
-  </si>
-  <si>
-    <t>user_55</t>
-  </si>
-  <si>
-    <t>******193802132553</t>
-  </si>
-  <si>
-    <t>user_56</t>
-  </si>
-  <si>
-    <t>******19570313005X</t>
-  </si>
-  <si>
-    <t>user_10</t>
-  </si>
-  <si>
-    <t>******196507165740</t>
-  </si>
-  <si>
     <t>东街</t>
   </si>
   <si>
-    <t>user_16</t>
-  </si>
-  <si>
-    <t>******196205066053</t>
-  </si>
-  <si>
-    <t>user_57</t>
-  </si>
-  <si>
-    <t>******19520512049X</t>
-  </si>
-  <si>
     <t>南街</t>
   </si>
   <si>
-    <t>user_58</t>
-  </si>
-  <si>
-    <t>******196207167827</t>
-  </si>
-  <si>
-    <t>user_59</t>
-  </si>
-  <si>
-    <t>******19390602344X</t>
-  </si>
-  <si>
     <t>北街</t>
   </si>
   <si>
-    <t>user_60</t>
-  </si>
-  <si>
-    <t>******196511280015</t>
-  </si>
-  <si>
-    <t>user_61</t>
-  </si>
-  <si>
-    <t>******195608282565</t>
-  </si>
-  <si>
-    <t>user_62</t>
-  </si>
-  <si>
-    <t>******194202037258</t>
-  </si>
-  <si>
-    <t>user_63</t>
-  </si>
-  <si>
-    <t>******194206142418</t>
-  </si>
-  <si>
-    <t>user_64</t>
-  </si>
-  <si>
-    <t>******196509093544</t>
-  </si>
-  <si>
-    <t>精神残疾</t>
-  </si>
-  <si>
     <t>项山路</t>
   </si>
   <si>
-    <t>user_20</t>
-  </si>
-  <si>
-    <t>******193505027503</t>
-  </si>
-  <si>
-    <t>user_65</t>
-  </si>
-  <si>
-    <t>******19590129256X</t>
-  </si>
-  <si>
-    <t>user_66</t>
-  </si>
-  <si>
-    <t>******196212010066</t>
-  </si>
-  <si>
-    <t>user_67</t>
-  </si>
-  <si>
-    <t>******194209293545</t>
-  </si>
-  <si>
     <t>石岭大道</t>
   </si>
   <si>
-    <t>user_68</t>
-  </si>
-  <si>
-    <t>******19630428008X</t>
-  </si>
-  <si>
     <t>滨河路</t>
   </si>
   <si>
-    <t>user_69</t>
-  </si>
-  <si>
-    <t>******196304081013</t>
-  </si>
-  <si>
     <t>代家湾</t>
   </si>
   <si>
-    <t>user_70</t>
-  </si>
-  <si>
-    <t>******196503057796</t>
-  </si>
-  <si>
-    <t>user_71</t>
-  </si>
-  <si>
-    <t>******194501080205</t>
-  </si>
-  <si>
-    <t>user_72</t>
-  </si>
-  <si>
-    <t>******194504166522</t>
-  </si>
-  <si>
-    <t>user_73</t>
-  </si>
-  <si>
-    <t>******195002235895</t>
-  </si>
-  <si>
-    <t>user_21</t>
-  </si>
-  <si>
-    <t>******193901040021</t>
-  </si>
-  <si>
     <t>上城壕</t>
   </si>
   <si>
-    <t>user_74</t>
-  </si>
-  <si>
-    <t>******194510092574</t>
-  </si>
-  <si>
-    <t>user_75</t>
-  </si>
-  <si>
-    <t>******195008162367</t>
-  </si>
-  <si>
     <t>板桥街</t>
   </si>
   <si>
-    <t>user_76</t>
-  </si>
-  <si>
-    <t>******196408260059</t>
-  </si>
-  <si>
-    <t>user_77</t>
-  </si>
-  <si>
-    <t>******195805130034</t>
-  </si>
-  <si>
-    <t>user_15</t>
-  </si>
-  <si>
-    <t>******195205050014</t>
-  </si>
-  <si>
     <t>新市街</t>
   </si>
   <si>
-    <t>user_78</t>
-  </si>
-  <si>
-    <t>******195905063721</t>
-  </si>
-  <si>
-    <t>user_79</t>
-  </si>
-  <si>
-    <t>******195604100015</t>
-  </si>
-  <si>
-    <t>user_80</t>
-  </si>
-  <si>
-    <t>******196312165532</t>
-  </si>
-  <si>
     <t>鱼禅寺</t>
   </si>
   <si>
-    <t>user_81</t>
-  </si>
-  <si>
-    <t>******196312090024</t>
-  </si>
-  <si>
     <t>学坝街</t>
   </si>
   <si>
-    <t>user_26</t>
-  </si>
-  <si>
-    <t>******19630714725X</t>
-  </si>
-  <si>
-    <t>user_82</t>
-  </si>
-  <si>
-    <t>******196306110025</t>
-  </si>
-  <si>
     <t>牌立湾</t>
   </si>
   <si>
-    <t>user_83</t>
-  </si>
-  <si>
-    <t>******195001090495</t>
-  </si>
-  <si>
     <t>其他</t>
-  </si>
-  <si>
-    <t>user_84</t>
-  </si>
-  <si>
-    <t>******195804293536</t>
-  </si>
-  <si>
-    <t>user_85</t>
-  </si>
-  <si>
-    <t>******196207153433</t>
-  </si>
-  <si>
-    <t>user_86</t>
-  </si>
-  <si>
-    <t>******196210313434</t>
-  </si>
-  <si>
-    <t>user_87</t>
-  </si>
-  <si>
-    <t>******195607093471</t>
-  </si>
-  <si>
-    <t>user_88</t>
-  </si>
-  <si>
-    <t>******195209162419</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -603,25 +586,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -659,7 +634,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -693,7 +668,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -728,10 +702,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -904,12 +877,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="4" max="4" width="36.85546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
@@ -963,31 +933,31 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="E2">
         <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -1001,34 +971,34 @@
         <v>18834</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="E3">
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -1042,34 +1012,34 @@
         <v>18474</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="E4">
         <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -1083,34 +1053,34 @@
         <v>18508</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E5">
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -1124,34 +1094,34 @@
         <v>18688</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>95</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -1165,34 +1135,34 @@
         <v>19301</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -1206,34 +1176,34 @@
         <v>18236</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="E8">
         <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -1247,34 +1217,34 @@
         <v>18464</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="E9">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -1288,34 +1258,34 @@
         <v>18747</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="E10">
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -1329,34 +1299,34 @@
         <v>18443</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="E11">
         <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -1370,34 +1340,34 @@
         <v>18471</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="E12">
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="M12">
         <v>1</v>
@@ -1411,34 +1381,34 @@
         <v>18713</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="E13">
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="M13">
         <v>2</v>
@@ -1452,34 +1422,34 @@
         <v>18840</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E14">
         <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L14" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="M14">
         <v>2</v>
@@ -1493,34 +1463,34 @@
         <v>18490</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L15" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="M15">
         <v>2</v>
@@ -1534,34 +1504,34 @@
         <v>18506</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="E16">
         <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L16" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="M16">
         <v>3</v>
@@ -1575,34 +1545,34 @@
         <v>19272</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E17">
         <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L17" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="M17">
         <v>4</v>
@@ -1616,34 +1586,34 @@
         <v>18255</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L18" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -1657,34 +1627,34 @@
         <v>19215</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E19">
         <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L19" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -1698,34 +1668,34 @@
         <v>18253</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E20">
         <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K20" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L20" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -1739,34 +1709,34 @@
         <v>19235</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E21">
         <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -1780,34 +1750,34 @@
         <v>18450</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E22">
         <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L22" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -1821,34 +1791,34 @@
         <v>18693</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E23">
         <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K23" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L23" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -1862,34 +1832,34 @@
         <v>18462</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E24">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H24">
         <v>100</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K24" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L24" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -1903,34 +1873,34 @@
         <v>18620</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E25">
         <v>60</v>
       </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H25">
         <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L25" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="M25">
         <v>11</v>
@@ -1944,34 +1914,34 @@
         <v>18821</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E26">
         <v>63</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H26">
         <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K26" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L26" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="M26">
         <v>11</v>
@@ -1985,34 +1955,34 @@
         <v>18762</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="E27">
         <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K27" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L27" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="M27">
         <v>12</v>
@@ -2026,34 +1996,34 @@
         <v>18823</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>63</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K28" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="M28">
         <v>12</v>
@@ -2067,34 +2037,34 @@
         <v>18382</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E29">
         <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H29">
         <v>100</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K29" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L29" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="M29">
         <v>13</v>
@@ -2108,34 +2078,34 @@
         <v>18261</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E30">
         <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H30">
         <v>100</v>
       </c>
       <c r="I30" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L30" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="M30">
         <v>13</v>
@@ -2149,34 +2119,34 @@
         <v>19273</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E31">
         <v>69</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K31" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L31" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="M31">
         <v>13</v>
@@ -2190,34 +2160,34 @@
         <v>19187</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E32">
         <v>83</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H32">
         <v>100</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L32" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="M32">
         <v>13</v>
@@ -2231,34 +2201,34 @@
         <v>18386</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E33">
         <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K33" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L33" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="M33">
         <v>13</v>
@@ -2272,34 +2242,34 @@
         <v>18504</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E34">
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H34">
         <v>100</v>
       </c>
       <c r="I34" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L34" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="M34">
         <v>20</v>
@@ -2313,34 +2283,34 @@
         <v>18377</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E35">
         <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H35">
         <v>100</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K35" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L35" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="M35">
         <v>20</v>
@@ -2354,34 +2324,34 @@
         <v>18812</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E36">
         <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K36" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="M36">
         <v>20</v>
@@ -2395,34 +2365,34 @@
         <v>18254</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37">
         <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H37">
         <v>100</v>
       </c>
       <c r="I37" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K37" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L37" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="M37">
         <v>20</v>
@@ -2436,7 +2406,7 @@
         <v>19189</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
         <v>110</v>
@@ -2445,25 +2415,25 @@
         <v>83</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H38">
         <v>100</v>
       </c>
       <c r="I38" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K38" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L38" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="M38">
         <v>21</v>
@@ -2477,34 +2447,34 @@
         <v>18833</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E39">
         <v>62</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H39">
         <v>100</v>
       </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K39" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="M39">
         <v>22</v>
@@ -2518,34 +2488,34 @@
         <v>18830</v>
       </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="D40" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E40">
         <v>62</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G40" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H40">
         <v>100</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L40" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M40">
         <v>30</v>
@@ -2559,34 +2529,34 @@
         <v>18259</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E41">
         <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H41">
         <v>100</v>
       </c>
       <c r="I41" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K41" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L41" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M41">
         <v>30</v>
@@ -2600,34 +2570,34 @@
         <v>19198</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E42">
         <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H42">
         <v>100</v>
       </c>
       <c r="I42" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K42" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L42" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M42">
         <v>30</v>
@@ -2641,34 +2611,34 @@
         <v>18394</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E43">
         <v>80</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H43">
         <v>100</v>
       </c>
       <c r="I43" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J43" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L43" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M43">
         <v>30</v>
@@ -2682,34 +2652,34 @@
         <v>18233</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E44">
         <v>75</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H44">
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K44" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L44" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M44">
         <v>30</v>
@@ -2723,34 +2693,34 @@
         <v>18699</v>
       </c>
       <c r="C45" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E45">
         <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H45">
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K45" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L45" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="M45">
         <v>31</v>
@@ -2764,34 +2734,34 @@
         <v>18226</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="D46" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E46">
         <v>80</v>
       </c>
       <c r="F46" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H46">
         <v>100</v>
       </c>
       <c r="I46" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J46" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K46" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L46" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="M46">
         <v>31</v>
@@ -2805,34 +2775,34 @@
         <v>18745</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E47">
         <v>75</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H47">
         <v>100</v>
       </c>
       <c r="I47" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="J47" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K47" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L47" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="M47">
         <v>32</v>
@@ -2846,34 +2816,34 @@
         <v>18499</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E48">
         <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H48">
         <v>100</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J48" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K48" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L48" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="M48">
         <v>32</v>
@@ -2887,34 +2857,34 @@
         <v>18470</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="D49" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E49">
         <v>67</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H49">
         <v>100</v>
       </c>
       <c r="I49" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J49" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K49" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L49" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="M49">
         <v>32</v>
@@ -2928,34 +2898,34 @@
         <v>18761</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="D50" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="E50">
         <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H50">
         <v>100</v>
       </c>
       <c r="I50" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J50" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K50" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L50" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="M50">
         <v>33</v>
@@ -2969,34 +2939,34 @@
         <v>18252</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E51">
         <v>66</v>
       </c>
       <c r="F51" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H51">
         <v>100</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J51" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K51" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L51" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="M51">
         <v>33</v>
@@ -3010,34 +2980,34 @@
         <v>18796</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E52">
         <v>69</v>
       </c>
       <c r="F52" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H52">
         <v>100</v>
       </c>
       <c r="I52" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J52" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K52" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L52" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="M52">
         <v>33</v>
@@ -3051,34 +3021,34 @@
         <v>18492</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E53">
         <v>62</v>
       </c>
       <c r="F53" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H53">
         <v>100</v>
       </c>
       <c r="I53" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="J53" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K53" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L53" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="M53">
         <v>34</v>
@@ -3092,34 +3062,34 @@
         <v>19302</v>
       </c>
       <c r="C54" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="D54" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="E54">
         <v>62</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H54">
         <v>100</v>
       </c>
       <c r="I54" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J54" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K54" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L54" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="M54">
         <v>35</v>
@@ -3133,34 +3103,34 @@
         <v>19299</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E55">
         <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H55">
         <v>100</v>
       </c>
       <c r="I55" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J55" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K55" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L55" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="M55">
         <v>35</v>
@@ -3174,34 +3144,34 @@
         <v>18487</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D56" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E56">
         <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H56">
         <v>100</v>
       </c>
       <c r="I56" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J56" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K56" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="M56">
         <v>36</v>
@@ -3215,34 +3185,34 @@
         <v>18743</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="D57" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="E57">
         <v>75</v>
       </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H57">
         <v>100</v>
       </c>
       <c r="I57" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="J57" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K57" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L57" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M57">
         <v>999</v>
@@ -3256,34 +3226,34 @@
         <v>19290</v>
       </c>
       <c r="C58" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="E58">
         <v>67</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H58">
         <v>100</v>
       </c>
       <c r="I58" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J58" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K58" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L58" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M58">
         <v>999</v>
@@ -3297,34 +3267,34 @@
         <v>19295</v>
       </c>
       <c r="C59" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="E59">
         <v>63</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G59" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H59">
         <v>100</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J59" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K59" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L59" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M59">
         <v>999</v>
@@ -3338,34 +3308,34 @@
         <v>18478</v>
       </c>
       <c r="C60" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="E60">
         <v>63</v>
       </c>
       <c r="F60" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H60">
         <v>100</v>
       </c>
       <c r="I60" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J60" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K60" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L60" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M60">
         <v>999</v>
@@ -3379,34 +3349,34 @@
         <v>19271</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="E61">
         <v>69</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G61" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H61">
         <v>100</v>
       </c>
       <c r="I61" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="J61" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K61" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L61" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M61">
         <v>999</v>
@@ -3420,34 +3390,34 @@
         <v>19243</v>
       </c>
       <c r="C62" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="E62">
         <v>73</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H62">
         <v>100</v>
       </c>
       <c r="I62" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="J62" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="K62" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="L62" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M62">
         <v>999</v>
@@ -3459,21 +3429,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -3621,8 +3576,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96F191B-40CB-4280-810C-3CC329D70378}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0986068F-8A5B-49EE-9F40-A58DB927B2D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3630,5 +3600,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0986068F-8A5B-49EE-9F40-A58DB927B2D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96F191B-40CB-4280-810C-3CC329D70378}"/>
 </file>